--- a/docs/design/monster-definitions.xlsx
+++ b/docs/design/monster-definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Pretty_Knights\docs\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBE9966-9A43-4557-988C-1A0B2FA358E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0763CE43-C291-42E1-9811-DC0880D5D8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기준" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="96">
   <si>
     <t>플레이어 기준값</t>
   </si>
@@ -72,19 +72,10 @@
     <t>Lv1→2 필요 경험치</t>
   </si>
   <si>
-    <t>25 × 1^1.6</t>
-  </si>
-  <si>
     <t>Lv2→3 필요 경험치</t>
   </si>
   <si>
-    <t>25 × 2^1.6</t>
-  </si>
-  <si>
     <t>Lv3→4 필요 경험치</t>
-  </si>
-  <si>
-    <t>25 × 3^1.6</t>
   </si>
   <si>
     <t>파란 글씨 = 직접 입력하는 값 · 회색 칸 = 수식(고치지 말 것) · 노란 칸 = 밸런싱 핵심</t>
@@ -322,6 +313,500 @@
   </si>
   <si>
     <t>Elite</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>50 * 2^1.8</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>50 * 1^1.8</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>50 * 3^1.8</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>경험치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>공식</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>현재레벨</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)^1.8</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>방어력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>공식</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>(ATK - DEF*1.5) = DAMAGE</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lv1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>공격력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>스킬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>시스템</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>플레이어는</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>온전히</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>스킬에</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>의존해</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>공격력이나</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>방어력을</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>올릴</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>있다</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>플레이어는</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>공격력이나</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>방어력</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>등의</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>수치를</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">레벨업을 통해서는 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>올릴</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t>없다</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -329,7 +814,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,6 +879,38 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -418,7 +935,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -441,11 +958,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -469,6 +997,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -771,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -805,7 +1337,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>6</v>
@@ -838,32 +1370,74 @@
         <v>11</v>
       </c>
       <c r="B8" s="5">
-        <v>25</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>12</v>
+        <v>50</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="5">
-        <v>76</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>14</v>
+        <v>174</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" s="5">
-        <v>145</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>16</v>
+        <v>361</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="17">
+        <v>50</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="17">
+        <v>20</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="17">
+        <v>0</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -895,105 +1469,105 @@
   <sheetData>
     <row r="1" spans="1:23" ht="19.5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="U5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="V5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="W5" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F6" s="7">
         <v>10</v>
@@ -1040,35 +1614,35 @@
       </c>
       <c r="T6" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G6,0),"")</f>
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="U6" s="10">
         <f t="shared" ref="U6" si="1">IFERROR(ROUND(T6*P6,1),"")</f>
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="V6" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S6,0),"")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W6" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F7" s="7">
         <v>15</v>
@@ -1115,35 +1689,35 @@
       </c>
       <c r="T7" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G7,0),"")</f>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="U7" s="10">
         <f>IFERROR(ROUND(T7*P7,1),"")</f>
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="V7" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S7,0),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7">
         <v>15</v>
@@ -1190,35 +1764,35 @@
       </c>
       <c r="T8" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G8,0),"")</f>
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="U8" s="10">
         <f>IFERROR(ROUND(T8*P8,1),"")</f>
-        <v>8.4</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="V8" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S8,0),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F9" s="7">
         <v>80</v>
@@ -1265,35 +1839,35 @@
       </c>
       <c r="T9" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G9,0),"")</f>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="U9" s="10">
         <f>IFERROR(ROUND(T9*P9,1),"")</f>
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="V9" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S9,0),"")</f>
         <v>1</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F10" s="7">
         <v>20</v>
@@ -1340,35 +1914,35 @@
       </c>
       <c r="T10" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G10,0),"")</f>
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="U10" s="10">
         <f>IFERROR(ROUND(T10*P10,1),"")</f>
-        <v>12.6</v>
+        <v>61.2</v>
       </c>
       <c r="V10" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S10,0),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W10" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>56</v>
       </c>
       <c r="F11" s="7">
         <v>35</v>
@@ -1415,35 +1989,35 @@
       </c>
       <c r="T11" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G11,0),"")</f>
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="U11" s="10">
         <f>IFERROR(ROUND(T11*P11,1),"")</f>
-        <v>7.2</v>
+        <v>30.6</v>
       </c>
       <c r="V11" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S11,0),"")</f>
         <v>1</v>
       </c>
       <c r="W11" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F12" s="7">
         <v>180</v>
@@ -1490,35 +2064,35 @@
       </c>
       <c r="T12" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G12,0),"")</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U12" s="10">
         <f>IFERROR(ROUND(T12*P12,1),"")</f>
-        <v>4.4000000000000004</v>
+        <v>22</v>
       </c>
       <c r="V12" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S12,0),"")</f>
         <v>1</v>
       </c>
       <c r="W12" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F13" s="7">
         <v>10</v>
@@ -1565,35 +2139,35 @@
       </c>
       <c r="T13" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G13,0),"")</f>
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="U13" s="10">
         <f>IFERROR(ROUND(T13*P13,1),"")</f>
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="V13" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S13,0),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W13" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F14" s="7">
         <v>15</v>
@@ -1640,35 +2214,35 @@
       </c>
       <c r="T14" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G14,0),"")</f>
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="U14" s="10">
         <f>IFERROR(ROUND(T14*P14,1),"")</f>
-        <v>17.5</v>
+        <v>85</v>
       </c>
       <c r="V14" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S14,0),"")</f>
         <v>1</v>
       </c>
       <c r="W14" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F15" s="7">
         <v>100</v>
@@ -1715,38 +2289,38 @@
       </c>
       <c r="T15" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$5/G15,0),"")</f>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="U15" s="10">
         <f>IFERROR(ROUND(T15*P15,1),"")</f>
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="V15" s="10">
         <f>IFERROR(ROUNDUP(기준!$B$8/S15,0),"")</f>
         <v>1</v>
       </c>
       <c r="W15" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
@@ -1754,12 +2328,12 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
